--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.144</v>
+        <v>0.122</v>
       </c>
       <c r="E2">
-        <v>0.017</v>
+        <v>0.04228999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1282520862440056</v>
+        <v>0.1828318060892699</v>
       </c>
       <c r="H2">
-        <v>0.1282520862440056</v>
+        <v>0.1828318060892699</v>
       </c>
       <c r="I2">
-        <v>0.1412415511837783</v>
+        <v>0.09998226426248891</v>
       </c>
       <c r="J2">
-        <v>0.0980824368415792</v>
+        <v>0.07543833841706035</v>
       </c>
       <c r="K2">
-        <v>13.229</v>
+        <v>6.568</v>
       </c>
       <c r="L2">
-        <v>0.04995279990937582</v>
+        <v>0.0388294413242684</v>
       </c>
       <c r="M2">
-        <v>6.4</v>
+        <v>4.98</v>
       </c>
       <c r="N2">
-        <v>0.03644024369412971</v>
+        <v>0.04999498042365224</v>
       </c>
       <c r="O2">
-        <v>0.4837856224960315</v>
+        <v>0.7582216808769793</v>
       </c>
       <c r="P2">
-        <v>6.4</v>
+        <v>4.98</v>
       </c>
       <c r="Q2">
-        <v>0.03644024369412971</v>
+        <v>0.04999498042365224</v>
       </c>
       <c r="R2">
-        <v>0.4837856224960315</v>
+        <v>0.7582216808769793</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.581</v>
+        <v>6.96</v>
       </c>
       <c r="V2">
-        <v>0.06024597164493537</v>
+        <v>0.06987250276076699</v>
       </c>
       <c r="W2">
-        <v>0.07035175879396985</v>
+        <v>0.06147186147186146</v>
       </c>
       <c r="X2">
-        <v>0.153042320411565</v>
+        <v>0.2678738955817576</v>
       </c>
       <c r="Y2">
-        <v>-0.08269056161759517</v>
+        <v>-0.2064020341098961</v>
       </c>
       <c r="Z2">
-        <v>1.288961355008274</v>
+        <v>0.7548205432565944</v>
       </c>
       <c r="AA2">
-        <v>0.06750086060118177</v>
+        <v>0.07245155855096883</v>
       </c>
       <c r="AB2">
-        <v>0.146368562697984</v>
+        <v>0.2582221224040965</v>
       </c>
       <c r="AC2">
-        <v>-0.07723222989220679</v>
+        <v>-0.1857705638531277</v>
       </c>
       <c r="AD2">
-        <v>68.164</v>
+        <v>53.419</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>68.164</v>
+        <v>53.419</v>
       </c>
       <c r="AG2">
-        <v>57.583</v>
+        <v>46.459</v>
       </c>
       <c r="AH2">
-        <v>0.2795967086966866</v>
+        <v>0.3490776258094871</v>
       </c>
       <c r="AI2">
-        <v>0.2605916490171041</v>
+        <v>0.3582306748301692</v>
       </c>
       <c r="AJ2">
-        <v>0.2469116215648356</v>
+        <v>0.3180620117889491</v>
       </c>
       <c r="AK2">
-        <v>0.229420740817473</v>
+        <v>0.3268101210616282</v>
       </c>
       <c r="AL2">
-        <v>11.887</v>
+        <v>10.778</v>
       </c>
       <c r="AM2">
-        <v>11.887</v>
+        <v>10.778</v>
       </c>
       <c r="AN2">
-        <v>1.670235965793536</v>
+        <v>2.825355688369387</v>
       </c>
       <c r="AO2">
-        <v>3.146714898628754</v>
+        <v>1.56912228613843</v>
       </c>
       <c r="AP2">
-        <v>1.410967631275881</v>
+        <v>2.457238059977786</v>
       </c>
       <c r="AQ2">
-        <v>3.146714898628754</v>
+        <v>1.56912228613843</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Softlogic Capital PLC (COSE:SCAP.N0000)</t>
+          <t>Arpico Insurance PLC (COSE:AINS.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.182</v>
+        <v>0.2</v>
       </c>
       <c r="E3">
-        <v>0.0175</v>
+        <v>0.265</v>
       </c>
       <c r="G3">
-        <v>0.1441048034934498</v>
+        <v>0.2677824267782427</v>
       </c>
       <c r="H3">
-        <v>0.1441048034934498</v>
+        <v>0.2677824267782427</v>
       </c>
       <c r="I3">
-        <v>0.1947598253275109</v>
+        <v>0.1729428172942817</v>
       </c>
       <c r="J3">
-        <v>0.1346134086822502</v>
+        <v>0.145096092475711</v>
       </c>
       <c r="K3">
-        <v>4.08</v>
+        <v>0.986</v>
       </c>
       <c r="L3">
-        <v>0.03563318777292576</v>
+        <v>0.1375174337517434</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,73 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.57</v>
+        <v>0.729</v>
       </c>
       <c r="V3">
-        <v>0.1077830188679245</v>
+        <v>0.178239608801956</v>
       </c>
       <c r="W3">
-        <v>0.1581395348837209</v>
+        <v>0.1048936170212766</v>
       </c>
       <c r="X3">
-        <v>0.2876913163166047</v>
+        <v>0.2761244686574209</v>
       </c>
       <c r="Y3">
-        <v>-0.1295517814328838</v>
+        <v>-0.1712308516361443</v>
       </c>
       <c r="Z3">
-        <v>1.931185697419464</v>
+        <v>0.740779006095671</v>
       </c>
       <c r="AA3">
-        <v>0.2599634895280427</v>
+        <v>0.1074841391725227</v>
       </c>
       <c r="AB3">
-        <v>0.1637149192375993</v>
+        <v>0.2605369005261077</v>
       </c>
       <c r="AC3">
-        <v>0.09624857029044334</v>
+        <v>-0.153052761353585</v>
       </c>
       <c r="AD3">
-        <v>62.4</v>
+        <v>0.595</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>62.4</v>
+        <v>0.595</v>
       </c>
       <c r="AG3">
-        <v>57.83</v>
+        <v>-0.134</v>
       </c>
       <c r="AH3">
-        <v>0.5954198473282443</v>
+        <v>0.1270010672358591</v>
       </c>
       <c r="AI3">
-        <v>0.5093877551020408</v>
+        <v>0.09527622097678141</v>
       </c>
       <c r="AJ3">
-        <v>0.57697296218697</v>
+        <v>-0.03387259858442872</v>
       </c>
       <c r="AK3">
-        <v>0.4903756465699991</v>
+        <v>-0.0242929659173314</v>
       </c>
       <c r="AL3">
-        <v>11.6</v>
+        <v>0.065</v>
       </c>
       <c r="AM3">
-        <v>11.6</v>
+        <v>0.065</v>
       </c>
       <c r="AN3">
-        <v>2.589211618257261</v>
+        <v>0.4507575757575757</v>
       </c>
       <c r="AO3">
-        <v>1.922413793103448</v>
+        <v>19.07692307692308</v>
       </c>
       <c r="AP3">
-        <v>2.399585062240664</v>
+        <v>-0.1015151515151515</v>
       </c>
       <c r="AQ3">
-        <v>1.922413793103448</v>
+        <v>19.07692307692308</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arpico Insurance PLC (COSE:AINS.N0000)</t>
+          <t>Union Assurance PLC (COSE:UAL.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,118 +853,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.262</v>
+        <v>0.122</v>
       </c>
       <c r="E4">
-        <v>0.327</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G4">
-        <v>0.1411290322580645</v>
+        <v>0.2150882825040129</v>
       </c>
       <c r="H4">
-        <v>0.1411290322580645</v>
+        <v>0.2150882825040129</v>
       </c>
       <c r="I4">
-        <v>0.1161290322580645</v>
+        <v>0.1157303370786517</v>
       </c>
       <c r="J4">
-        <v>0.06836769342711617</v>
+        <v>0.08791917080393694</v>
       </c>
       <c r="K4">
-        <v>0.781</v>
+        <v>5.88</v>
       </c>
       <c r="L4">
-        <v>0.06298387096774194</v>
+        <v>0.09438202247191012</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>3.55</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.07924107142857142</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.6037414965986394</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>3.55</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.07924107142857142</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.6037414965986394</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.522</v>
+        <v>1.99</v>
       </c>
       <c r="V4">
-        <v>0.06177514792899409</v>
+        <v>0.04441964285714286</v>
       </c>
       <c r="W4">
-        <v>0.08388829215896886</v>
+        <v>0.08305084745762711</v>
       </c>
       <c r="X4">
-        <v>0.153042320411565</v>
+        <v>0.2580804132227738</v>
       </c>
       <c r="Y4">
-        <v>-0.06915402825259616</v>
+        <v>-0.1750295657651466</v>
       </c>
       <c r="Z4">
-        <v>1.752650176678445</v>
+        <v>0.8838133068520357</v>
       </c>
       <c r="AA4">
-        <v>0.1198246499641329</v>
+        <v>0.07770413308391647</v>
       </c>
       <c r="AB4">
-        <v>0.146368562697984</v>
+        <v>0.2546972096845907</v>
       </c>
       <c r="AC4">
-        <v>-0.02654391273385109</v>
+        <v>-0.1769930766006742</v>
       </c>
       <c r="AD4">
-        <v>0.801</v>
+        <v>1.54</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.801</v>
+        <v>1.54</v>
       </c>
       <c r="AG4">
-        <v>0.279</v>
+        <v>-0.45</v>
       </c>
       <c r="AH4">
-        <v>0.08658523402875366</v>
+        <v>0.03323262839879154</v>
       </c>
       <c r="AI4">
-        <v>0.07852171355749436</v>
+        <v>0.04357668364459537</v>
       </c>
       <c r="AJ4">
-        <v>0.03196242410356284</v>
+        <v>-0.01014656144306652</v>
       </c>
       <c r="AK4">
-        <v>0.02882529186899473</v>
+        <v>-0.01349325337331334</v>
       </c>
       <c r="AL4">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.5101910828025478</v>
-      </c>
-      <c r="AO4">
-        <v>13.09090909090909</v>
+        <v>0.1898890258939581</v>
       </c>
       <c r="AP4">
-        <v>0.1777070063694268</v>
-      </c>
-      <c r="AQ4">
-        <v>13.09090909090909</v>
+        <v>-0.05548705302096178</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Union Assurance PLC (COSE:UAL.N0000)</t>
+          <t>Amãna Takaful Life PLC (COSE:ATLL.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,115 +981,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.144</v>
+        <v>0.0624</v>
       </c>
       <c r="E5">
-        <v>0.0165</v>
+        <v>-0.00632</v>
       </c>
       <c r="G5">
-        <v>0.09910000000000001</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H5">
-        <v>0.09910000000000001</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="I5">
-        <v>0.0892</v>
+        <v>0.0455026455026455</v>
       </c>
       <c r="J5">
-        <v>0.05210323928944618</v>
+        <v>0.0455026455026455</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>0.142</v>
       </c>
       <c r="L5">
-        <v>0.05599999999999999</v>
+        <v>0.03756613756613757</v>
       </c>
       <c r="M5">
-        <v>4.13</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04813519813519813</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.7375</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>4.13</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.04813519813519813</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.7375</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>3.15</v>
+        <v>0.169</v>
       </c>
       <c r="V5">
-        <v>0.03671328671328671</v>
+        <v>0.03912037037037037</v>
       </c>
       <c r="W5">
-        <v>0.07035175879396985</v>
+        <v>0.06147186147186146</v>
       </c>
       <c r="X5">
-        <v>0.1470093302755463</v>
+        <v>0.2678738955817576</v>
       </c>
       <c r="Y5">
-        <v>-0.07665757148157643</v>
+        <v>-0.2064020341098961</v>
       </c>
       <c r="Z5">
-        <v>1.29552138258042</v>
+        <v>1.592249368155013</v>
       </c>
       <c r="AA5">
-        <v>0.06750086060118177</v>
+        <v>0.07245155855096883</v>
       </c>
       <c r="AB5">
-        <v>0.1447330904933886</v>
+        <v>0.2582221224040965</v>
       </c>
       <c r="AC5">
-        <v>-0.07723222989220679</v>
+        <v>-0.1857705638531277</v>
       </c>
       <c r="AD5">
-        <v>2.84</v>
+        <v>0.409</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.84</v>
+        <v>0.409</v>
       </c>
       <c r="AG5">
-        <v>-0.3100000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="AH5">
-        <v>0.03203971119133574</v>
+        <v>0.08648762951998308</v>
       </c>
       <c r="AI5">
-        <v>0.03856599674090168</v>
+        <v>0.2200107584722969</v>
       </c>
       <c r="AJ5">
-        <v>-0.003626155105860336</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="AK5">
-        <v>-0.004397786920130516</v>
+        <v>0.1420118343195266</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AN5">
-        <v>0.2757281553398058</v>
+        <v>2.076142131979695</v>
+      </c>
+      <c r="AO5">
+        <v>5.548387096774193</v>
       </c>
       <c r="AP5">
-        <v>-0.03009708737864078</v>
+        <v>1.218274111675127</v>
+      </c>
+      <c r="AQ5">
+        <v>5.548387096774193</v>
       </c>
     </row>
     <row r="6">
@@ -1112,46 +1112,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.139</v>
+        <v>-0.0106</v>
       </c>
       <c r="E6">
-        <v>-0.164</v>
+        <v>-0.161</v>
       </c>
       <c r="G6">
-        <v>0.1812883435582822</v>
+        <v>0.3486033519553073</v>
       </c>
       <c r="H6">
-        <v>0.1812883435582822</v>
+        <v>0.3486033519553073</v>
       </c>
       <c r="I6">
-        <v>0.146319018404908</v>
+        <v>0.1340782122905028</v>
       </c>
       <c r="J6">
-        <v>0.08898201547536158</v>
+        <v>0.0903570561088171</v>
       </c>
       <c r="K6">
-        <v>2.83</v>
+        <v>1.55</v>
       </c>
       <c r="L6">
-        <v>0.08680981595092024</v>
+        <v>0.08659217877094973</v>
       </c>
       <c r="M6">
-        <v>2.27</v>
+        <v>1.43</v>
       </c>
       <c r="N6">
-        <v>0.06618075801749272</v>
+        <v>0.07333333333333333</v>
       </c>
       <c r="O6">
-        <v>0.8021201413427562</v>
+        <v>0.9225806451612902</v>
       </c>
       <c r="P6">
-        <v>2.27</v>
+        <v>1.43</v>
       </c>
       <c r="Q6">
-        <v>0.06618075801749272</v>
+        <v>0.07333333333333333</v>
       </c>
       <c r="R6">
-        <v>0.8021201413427562</v>
+        <v>0.9225806451612902</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1160,73 +1160,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.92</v>
+        <v>0.342</v>
       </c>
       <c r="V6">
-        <v>0.05597667638483965</v>
+        <v>0.01753846153846154</v>
       </c>
       <c r="W6">
-        <v>0.05380228136882129</v>
+        <v>0.03051181102362205</v>
       </c>
       <c r="X6">
-        <v>0.1484481472845317</v>
+        <v>0.2564537090069379</v>
       </c>
       <c r="Y6">
-        <v>-0.09464586591571039</v>
+        <v>-0.2259418979833158</v>
       </c>
       <c r="Z6">
-        <v>0.5515141262053799</v>
+        <v>0.3543151227236738</v>
       </c>
       <c r="AA6">
-        <v>0.04907483851288762</v>
+        <v>0.03201487142414541</v>
       </c>
       <c r="AB6">
-        <v>0.1451406247632579</v>
+        <v>0.2540715283412736</v>
       </c>
       <c r="AC6">
-        <v>-0.09606578625037027</v>
+        <v>-0.2220566569171281</v>
       </c>
       <c r="AD6">
-        <v>1.64</v>
+        <v>0.475</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.64</v>
+        <v>0.475</v>
       </c>
       <c r="AG6">
-        <v>-0.28</v>
+        <v>0.133</v>
       </c>
       <c r="AH6">
-        <v>0.04563160823594881</v>
+        <v>0.02377972465581977</v>
       </c>
       <c r="AI6">
-        <v>0.03127383676582761</v>
+        <v>0.01807802093244529</v>
       </c>
       <c r="AJ6">
-        <v>-0.008230452674897122</v>
+        <v>0.006774308562114805</v>
       </c>
       <c r="AK6">
-        <v>-0.005542359461599367</v>
+        <v>0.005128600624686691</v>
       </c>
       <c r="AL6">
-        <v>0.14</v>
+        <v>0.082</v>
       </c>
       <c r="AM6">
-        <v>0.14</v>
+        <v>0.082</v>
       </c>
       <c r="AN6">
-        <v>0.3388429752066116</v>
+        <v>0.1930894308943089</v>
       </c>
       <c r="AO6">
-        <v>34.07142857142856</v>
+        <v>29.26829268292683</v>
       </c>
       <c r="AP6">
-        <v>-0.0578512396694215</v>
+        <v>0.05406504065040649</v>
       </c>
       <c r="AQ6">
-        <v>34.07142857142856</v>
+        <v>29.26829268292683</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amãna Takaful Life PLC (COSE:ATLL.N0000)</t>
+          <t>Softlogic Capital PLC (COSE:SCAP.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,25 +1246,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0106</v>
+        <v>0.207</v>
       </c>
       <c r="G7">
-        <v>-0.01969981238273921</v>
+        <v>0.1184615384615385</v>
       </c>
       <c r="H7">
-        <v>-0.01969981238273921</v>
+        <v>0.1184615384615385</v>
       </c>
       <c r="I7">
-        <v>-0.004690431519699813</v>
+        <v>0.0755128205128205</v>
       </c>
       <c r="J7">
-        <v>-0.004690431519699813</v>
+        <v>0.03775641025641025</v>
       </c>
       <c r="K7">
-        <v>-0.062</v>
+        <v>-1.99</v>
       </c>
       <c r="L7">
-        <v>-0.01163227016885553</v>
+        <v>-0.02551282051282051</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1288,73 +1288,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.419</v>
+        <v>3.73</v>
       </c>
       <c r="V7">
-        <v>0.08952991452991453</v>
+        <v>0.1386617100371747</v>
       </c>
       <c r="W7">
-        <v>-0.02440944881889764</v>
+        <v>-0.05993975903614458</v>
       </c>
       <c r="X7">
-        <v>0.1538649610330593</v>
+        <v>0.5567901853583583</v>
       </c>
       <c r="Y7">
-        <v>-0.1782744098519569</v>
+        <v>-0.6167299443945029</v>
       </c>
       <c r="Z7">
-        <v>1.906294706723891</v>
+        <v>0.8568603757003186</v>
       </c>
       <c r="AA7">
-        <v>-0.00894134477825465</v>
+        <v>0.03235197187740305</v>
       </c>
       <c r="AB7">
-        <v>0.1469057183361885</v>
+        <v>0.295653348503892</v>
       </c>
       <c r="AC7">
-        <v>-0.1558470631144431</v>
+        <v>-0.2633013766264889</v>
       </c>
       <c r="AD7">
-        <v>0.483</v>
+        <v>50.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.483</v>
+        <v>50.4</v>
       </c>
       <c r="AG7">
-        <v>0.064</v>
+        <v>46.67</v>
       </c>
       <c r="AH7">
-        <v>0.09355026147588612</v>
+        <v>0.6520051746442432</v>
       </c>
       <c r="AI7">
-        <v>0.1729323308270677</v>
+        <v>0.6347607052896724</v>
       </c>
       <c r="AJ7">
-        <v>0.01349072512647555</v>
+        <v>0.6343618322685878</v>
       </c>
       <c r="AK7">
-        <v>0.02695871946082561</v>
+        <v>0.6167569710585437</v>
       </c>
       <c r="AL7">
-        <v>0.037</v>
+        <v>10.6</v>
       </c>
       <c r="AM7">
-        <v>0.037</v>
+        <v>10.6</v>
       </c>
       <c r="AN7">
-        <v>483</v>
+        <v>7.390029325513196</v>
       </c>
       <c r="AO7">
-        <v>-0.6756756756756758</v>
+        <v>0.5556603773584906</v>
       </c>
       <c r="AP7">
-        <v>64</v>
+        <v>6.843108504398827</v>
       </c>
       <c r="AQ7">
-        <v>-0.6756756756756758</v>
+        <v>0.5556603773584906</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.122</v>
+        <v>0.16</v>
       </c>
       <c r="E2">
-        <v>0.04228999999999999</v>
+        <v>-0.187</v>
       </c>
       <c r="G2">
-        <v>0.1828318060892699</v>
+        <v>0.1281363746663431</v>
       </c>
       <c r="H2">
-        <v>0.1828318060892699</v>
+        <v>0.1281363746663431</v>
       </c>
       <c r="I2">
-        <v>0.09998226426248891</v>
+        <v>0.1841381541696999</v>
       </c>
       <c r="J2">
-        <v>0.07543833841706035</v>
+        <v>0.1496372589659123</v>
       </c>
       <c r="K2">
-        <v>6.568</v>
+        <v>9.24</v>
       </c>
       <c r="L2">
-        <v>0.0388294413242684</v>
+        <v>0.03736957049259888</v>
       </c>
       <c r="M2">
-        <v>4.98</v>
+        <v>1.86</v>
       </c>
       <c r="N2">
-        <v>0.04999498042365224</v>
+        <v>0.01444435815795604</v>
       </c>
       <c r="O2">
-        <v>0.7582216808769793</v>
+        <v>0.2012987012987013</v>
       </c>
       <c r="P2">
-        <v>4.98</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>0.04999498042365224</v>
+        <v>0.01444435815795604</v>
       </c>
       <c r="R2">
-        <v>0.7582216808769793</v>
+        <v>0.2012987012987013</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.96</v>
+        <v>8.099</v>
       </c>
       <c r="V2">
-        <v>0.06987250276076699</v>
+        <v>0.06289508425875592</v>
       </c>
       <c r="W2">
-        <v>0.06147186147186146</v>
+        <v>0.1013793103448276</v>
       </c>
       <c r="X2">
-        <v>0.2678738955817576</v>
+        <v>0.2227370495029449</v>
       </c>
       <c r="Y2">
-        <v>-0.2064020341098961</v>
+        <v>-0.1213577391581173</v>
       </c>
       <c r="Z2">
-        <v>0.7548205432565944</v>
+        <v>1.93991793439459</v>
       </c>
       <c r="AA2">
-        <v>0.07245155855096883</v>
+        <v>0.2879320902928818</v>
       </c>
       <c r="AB2">
-        <v>0.2582221224040965</v>
+        <v>0.2160588744075815</v>
       </c>
       <c r="AC2">
-        <v>-0.1857705638531277</v>
+        <v>0.04290906152739754</v>
       </c>
       <c r="AD2">
-        <v>53.419</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>53.419</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="AG2">
-        <v>46.459</v>
+        <v>64.86099999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3490776258094871</v>
+        <v>0.3616715411688891</v>
       </c>
       <c r="AI2">
-        <v>0.3582306748301692</v>
+        <v>0.3383259911894273</v>
       </c>
       <c r="AJ2">
-        <v>0.3180620117889491</v>
+        <v>0.3349721893705037</v>
       </c>
       <c r="AK2">
-        <v>0.3268101210616282</v>
+        <v>0.3125063237469344</v>
       </c>
       <c r="AL2">
-        <v>10.778</v>
+        <v>22.262</v>
       </c>
       <c r="AM2">
-        <v>10.778</v>
+        <v>22.262</v>
       </c>
       <c r="AN2">
-        <v>2.825355688369387</v>
+        <v>1.525274909060501</v>
       </c>
       <c r="AO2">
-        <v>1.56912228613843</v>
+        <v>2.045189111490432</v>
       </c>
       <c r="AP2">
-        <v>2.457238059977786</v>
+        <v>1.355960195676715</v>
       </c>
       <c r="AQ2">
-        <v>1.56912228613843</v>
+        <v>2.045189111490432</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arpico Insurance PLC (COSE:AINS.N0000)</t>
+          <t>Janashakthi Insurance PLC (COSE:JINS.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.2</v>
+        <v>0.254</v>
       </c>
       <c r="E3">
-        <v>0.265</v>
+        <v>-0.185</v>
       </c>
       <c r="G3">
-        <v>0.2677824267782427</v>
+        <v>0.131042654028436</v>
       </c>
       <c r="H3">
-        <v>0.2677824267782427</v>
+        <v>0.131042654028436</v>
       </c>
       <c r="I3">
-        <v>0.1729428172942817</v>
+        <v>0.3104265402843602</v>
       </c>
       <c r="J3">
-        <v>0.145096092475711</v>
+        <v>0.259427894380501</v>
       </c>
       <c r="K3">
-        <v>0.986</v>
+        <v>10.5</v>
       </c>
       <c r="L3">
-        <v>0.1375174337517434</v>
+        <v>0.2488151658767772</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.86</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06888888888888889</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1771428571428572</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.86</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06888888888888889</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1771428571428572</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.729</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="V3">
-        <v>0.178239608801956</v>
+        <v>0.02988888888888889</v>
       </c>
       <c r="W3">
-        <v>0.1048936170212766</v>
+        <v>0.4069767441860465</v>
       </c>
       <c r="X3">
-        <v>0.2761244686574209</v>
+        <v>0.2198648235293288</v>
       </c>
       <c r="Y3">
-        <v>-0.1712308516361443</v>
+        <v>0.1871119206567178</v>
       </c>
       <c r="Z3">
-        <v>0.740779006095671</v>
+        <v>1.62727027339683</v>
       </c>
       <c r="AA3">
-        <v>0.1074841391725227</v>
+        <v>0.4221593006153218</v>
       </c>
       <c r="AB3">
-        <v>0.2605369005261077</v>
+        <v>0.2149275167404218</v>
       </c>
       <c r="AC3">
-        <v>-0.153052761353585</v>
+        <v>0.2072317838749</v>
       </c>
       <c r="AD3">
-        <v>0.595</v>
+        <v>1.78</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.595</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
-        <v>-0.134</v>
+        <v>0.973</v>
       </c>
       <c r="AH3">
-        <v>0.1270010672358591</v>
+        <v>0.06184850590687978</v>
       </c>
       <c r="AI3">
-        <v>0.09527622097678141</v>
+        <v>0.04093836246550138</v>
       </c>
       <c r="AJ3">
-        <v>-0.03387259858442872</v>
+        <v>0.0347835412719408</v>
       </c>
       <c r="AK3">
-        <v>-0.0242929659173314</v>
+        <v>0.02280130293159609</v>
       </c>
       <c r="AL3">
-        <v>0.065</v>
+        <v>0.464</v>
       </c>
       <c r="AM3">
-        <v>0.065</v>
+        <v>0.464</v>
       </c>
       <c r="AN3">
-        <v>0.4507575757575757</v>
+        <v>0.1328358208955224</v>
       </c>
       <c r="AO3">
-        <v>19.07692307692308</v>
+        <v>28.23275862068965</v>
       </c>
       <c r="AP3">
-        <v>-0.1015151515151515</v>
+        <v>0.07261194029850745</v>
       </c>
       <c r="AQ3">
-        <v>19.07692307692308</v>
+        <v>28.23275862068965</v>
       </c>
     </row>
     <row r="4">
@@ -853,103 +856,100 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.122</v>
+        <v>0.16</v>
       </c>
       <c r="E4">
-        <v>0.09089999999999999</v>
+        <v>-0.187</v>
       </c>
       <c r="G4">
-        <v>0.2150882825040129</v>
+        <v>0.1165158371040724</v>
       </c>
       <c r="H4">
-        <v>0.2150882825040129</v>
+        <v>0.1165158371040724</v>
       </c>
       <c r="I4">
-        <v>0.1157303370786517</v>
+        <v>0.1493212669683258</v>
       </c>
       <c r="J4">
-        <v>0.08791917080393694</v>
+        <v>0.1086259639283666</v>
       </c>
       <c r="K4">
-        <v>5.88</v>
+        <v>10.3</v>
       </c>
       <c r="L4">
-        <v>0.09438202247191012</v>
+        <v>0.1165158371040724</v>
       </c>
       <c r="M4">
-        <v>3.55</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07924107142857142</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6037414965986394</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>3.55</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.07924107142857142</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.6037414965986394</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="V4">
-        <v>0.04441964285714286</v>
+        <v>0.02691256830601093</v>
       </c>
       <c r="W4">
-        <v>0.08305084745762711</v>
+        <v>0.3047337278106509</v>
       </c>
       <c r="X4">
-        <v>0.2580804132227738</v>
+        <v>0.2140720960856576</v>
       </c>
       <c r="Y4">
-        <v>-0.1750295657651466</v>
+        <v>0.09066163172499336</v>
       </c>
       <c r="Z4">
-        <v>0.8838133068520357</v>
+        <v>2.650674662668666</v>
       </c>
       <c r="AA4">
-        <v>0.07770413308391647</v>
+        <v>0.2879320902928818</v>
       </c>
       <c r="AB4">
-        <v>0.2546972096845907</v>
+        <v>0.2124981191456513</v>
       </c>
       <c r="AC4">
-        <v>-0.1769930766006742</v>
+        <v>0.07543397114723049</v>
       </c>
       <c r="AD4">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AG4">
-        <v>-0.45</v>
+        <v>-0.3799999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.03323262839879154</v>
+        <v>0.02125952667468913</v>
       </c>
       <c r="AI4">
-        <v>0.04357668364459537</v>
+        <v>0.02324901301359848</v>
       </c>
       <c r="AJ4">
-        <v>-0.01014656144306652</v>
+        <v>-0.005218346608074703</v>
       </c>
       <c r="AK4">
-        <v>-0.01349325337331334</v>
+        <v>-0.005721168322794338</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.1898890258939581</v>
+        <v>0.1127659574468085</v>
       </c>
       <c r="AP4">
-        <v>-0.05548705302096178</v>
+        <v>-0.02695035460992907</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amãna Takaful Life PLC (COSE:ATLL.N0000)</t>
+          <t>Softlogic Capital PLC (COSE:SCAP.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,28 +981,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0624</v>
-      </c>
-      <c r="E5">
-        <v>-0.00632</v>
+        <v>0.193</v>
       </c>
       <c r="G5">
-        <v>0.03333333333333333</v>
+        <v>0.149706457925636</v>
       </c>
       <c r="H5">
-        <v>0.03333333333333333</v>
+        <v>0.149706457925636</v>
       </c>
       <c r="I5">
-        <v>0.0455026455026455</v>
+        <v>0.1819960861056752</v>
       </c>
       <c r="J5">
-        <v>0.0455026455026455</v>
+        <v>0.1819960861056752</v>
       </c>
       <c r="K5">
-        <v>0.142</v>
+        <v>-11.9</v>
       </c>
       <c r="L5">
-        <v>0.03756613756613757</v>
+        <v>-0.1164383561643836</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1011,7 +1008,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1020,79 +1017,79 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.169</v>
+        <v>4.69</v>
       </c>
       <c r="V5">
-        <v>0.03912037037037037</v>
+        <v>0.2392857142857143</v>
       </c>
       <c r="W5">
-        <v>0.06147186147186146</v>
+        <v>-0.8321678321678322</v>
       </c>
       <c r="X5">
-        <v>0.2678738955817576</v>
+        <v>0.6712150919166719</v>
       </c>
       <c r="Y5">
-        <v>-0.2064020341098961</v>
+        <v>-1.503382924084504</v>
       </c>
       <c r="Z5">
-        <v>1.592249368155013</v>
+        <v>1.676234213547646</v>
       </c>
       <c r="AA5">
-        <v>0.07245155855096883</v>
+        <v>0.3050680662620961</v>
       </c>
       <c r="AB5">
-        <v>0.2582221224040965</v>
+        <v>0.2621590047346986</v>
       </c>
       <c r="AC5">
-        <v>-0.1857705638531277</v>
+        <v>0.04290906152739754</v>
       </c>
       <c r="AD5">
-        <v>0.409</v>
+        <v>68.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.409</v>
+        <v>68.8</v>
       </c>
       <c r="AG5">
-        <v>0.24</v>
+        <v>64.11</v>
       </c>
       <c r="AH5">
-        <v>0.08648762951998308</v>
+        <v>0.7782805429864252</v>
       </c>
       <c r="AI5">
-        <v>0.2200107584722969</v>
+        <v>0.7303609341825903</v>
       </c>
       <c r="AJ5">
-        <v>0.0526315789473684</v>
+        <v>0.7658583203918289</v>
       </c>
       <c r="AK5">
-        <v>0.1420118343195266</v>
+        <v>0.7162328231482517</v>
       </c>
       <c r="AL5">
-        <v>0.031</v>
+        <v>21.7</v>
       </c>
       <c r="AM5">
-        <v>0.031</v>
+        <v>21.7</v>
       </c>
       <c r="AN5">
-        <v>2.076142131979695</v>
+        <v>3.510204081632653</v>
       </c>
       <c r="AO5">
-        <v>5.548387096774193</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="AP5">
-        <v>1.218274111675127</v>
+        <v>3.270918367346939</v>
       </c>
       <c r="AQ5">
-        <v>5.548387096774193</v>
+        <v>0.8571428571428572</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Janashakthi Insurance PLC (COSE:JINS.N0000)</t>
+          <t>Amãna Takaful Life PLC (COSE:ATLL.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,121 +1109,115 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0106</v>
-      </c>
-      <c r="E6">
-        <v>-0.161</v>
+        <v>0.113</v>
       </c>
       <c r="G6">
-        <v>0.3486033519553073</v>
+        <v>0.0349809885931559</v>
       </c>
       <c r="H6">
-        <v>0.3486033519553073</v>
+        <v>0.0349809885931559</v>
       </c>
       <c r="I6">
-        <v>0.1340782122905028</v>
+        <v>0.02908745247148289</v>
       </c>
       <c r="J6">
-        <v>0.0903570561088171</v>
+        <v>0.02908745247148289</v>
       </c>
       <c r="K6">
-        <v>1.55</v>
+        <v>0.147</v>
       </c>
       <c r="L6">
-        <v>0.08659217877094973</v>
+        <v>0.0279467680608365</v>
       </c>
       <c r="M6">
-        <v>1.43</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.07333333333333333</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.9225806451612902</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>1.43</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.07333333333333333</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.9225806451612902</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>0.342</v>
+        <v>0.076</v>
       </c>
       <c r="V6">
-        <v>0.01753846153846154</v>
+        <v>0.01743119266055046</v>
       </c>
       <c r="W6">
-        <v>0.03051181102362205</v>
+        <v>0.1013793103448276</v>
       </c>
       <c r="X6">
-        <v>0.2564537090069379</v>
+        <v>0.2227370495029449</v>
       </c>
       <c r="Y6">
-        <v>-0.2259418979833158</v>
+        <v>-0.1213577391581173</v>
       </c>
       <c r="Z6">
-        <v>0.3543151227236738</v>
+        <v>3.112426035502958</v>
       </c>
       <c r="AA6">
-        <v>0.03201487142414541</v>
+        <v>0.09053254437869823</v>
       </c>
       <c r="AB6">
-        <v>0.2540715283412736</v>
+        <v>0.2160588744075815</v>
       </c>
       <c r="AC6">
-        <v>-0.2220566569171281</v>
+        <v>-0.1255263300288832</v>
       </c>
       <c r="AD6">
-        <v>0.475</v>
+        <v>0.383</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.475</v>
+        <v>0.383</v>
       </c>
       <c r="AG6">
-        <v>0.133</v>
+        <v>0.307</v>
       </c>
       <c r="AH6">
-        <v>0.02377972465581977</v>
+        <v>0.08075057980181319</v>
       </c>
       <c r="AI6">
-        <v>0.01807802093244529</v>
+        <v>0.1722896986054881</v>
       </c>
       <c r="AJ6">
-        <v>0.006774308562114805</v>
+        <v>0.06578101564173987</v>
       </c>
       <c r="AK6">
-        <v>0.005128600624686691</v>
+        <v>0.1429902189101071</v>
       </c>
       <c r="AL6">
-        <v>0.082</v>
+        <v>0.022</v>
       </c>
       <c r="AM6">
-        <v>0.082</v>
+        <v>0.022</v>
       </c>
       <c r="AN6">
-        <v>0.1930894308943089</v>
+        <v>2.104395604395604</v>
       </c>
       <c r="AO6">
-        <v>29.26829268292683</v>
+        <v>6.954545454545455</v>
       </c>
       <c r="AP6">
-        <v>0.05406504065040649</v>
+        <v>1.686813186813187</v>
       </c>
       <c r="AQ6">
-        <v>29.26829268292683</v>
+        <v>6.954545454545455</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Softlogic Capital PLC (COSE:SCAP.N0000)</t>
+          <t>Arpico Insurance PLC (COSE:AINS.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,25 +1237,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.207</v>
+        <v>0.142</v>
+      </c>
+      <c r="E7">
+        <v>-0.221</v>
       </c>
       <c r="G7">
-        <v>0.1184615384615385</v>
+        <v>0.04010869565217392</v>
       </c>
       <c r="H7">
-        <v>0.1184615384615385</v>
+        <v>0.04010869565217392</v>
       </c>
       <c r="I7">
-        <v>0.0755128205128205</v>
+        <v>0.05184782608695652</v>
       </c>
       <c r="J7">
-        <v>0.03775641025641025</v>
+        <v>0.02592391304347826</v>
       </c>
       <c r="K7">
-        <v>-1.99</v>
+        <v>0.193</v>
       </c>
       <c r="L7">
-        <v>-0.02551282051282051</v>
+        <v>0.02097826086956522</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1273,7 +1267,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1282,79 +1276,79 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3.73</v>
+        <v>0.556</v>
       </c>
       <c r="V7">
-        <v>0.1386617100371747</v>
+        <v>0.1206073752711497</v>
       </c>
       <c r="W7">
-        <v>-0.05993975903614458</v>
+        <v>0.03415929203539823</v>
       </c>
       <c r="X7">
-        <v>0.5567901853583583</v>
+        <v>0.2227950096974284</v>
       </c>
       <c r="Y7">
-        <v>-0.6167299443945029</v>
+        <v>-0.1886357176620302</v>
       </c>
       <c r="Z7">
-        <v>0.8568603757003186</v>
+        <v>1.667875271936186</v>
       </c>
       <c r="AA7">
-        <v>0.03235197187740305</v>
+        <v>0.04323785351704133</v>
       </c>
       <c r="AB7">
-        <v>0.295653348503892</v>
+        <v>0.2160812356022809</v>
       </c>
       <c r="AC7">
-        <v>-0.2633013766264889</v>
+        <v>-0.1728433820852396</v>
       </c>
       <c r="AD7">
-        <v>50.4</v>
+        <v>0.407</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>50.4</v>
+        <v>0.407</v>
       </c>
       <c r="AG7">
-        <v>46.67</v>
+        <v>-0.1490000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.6520051746442432</v>
+        <v>0.0811241777954953</v>
       </c>
       <c r="AI7">
-        <v>0.6347607052896724</v>
+        <v>0.05532146255267092</v>
       </c>
       <c r="AJ7">
-        <v>0.6343618322685878</v>
+        <v>-0.03340058282896213</v>
       </c>
       <c r="AK7">
-        <v>0.6167569710585437</v>
+        <v>-0.02190854286134393</v>
       </c>
       <c r="AL7">
-        <v>10.6</v>
+        <v>0.076</v>
       </c>
       <c r="AM7">
-        <v>10.6</v>
+        <v>0.076</v>
       </c>
       <c r="AN7">
-        <v>7.390029325513196</v>
+        <v>0.7373188405797101</v>
       </c>
       <c r="AO7">
-        <v>0.5556603773584906</v>
+        <v>6.276315789473684</v>
       </c>
       <c r="AP7">
-        <v>6.843108504398827</v>
+        <v>-0.2699275362318842</v>
       </c>
       <c r="AQ7">
-        <v>0.5556603773584906</v>
+        <v>6.276315789473684</v>
       </c>
     </row>
   </sheetData>
